--- a/notice.xlsx
+++ b/notice.xlsx
@@ -461,7 +461,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -478,9 +478,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -446,15 +446,9 @@
         <v/>
       </c>
     </row>
-    <row r="3">
-      <c r="C3" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -428,7 +428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -441,14 +441,9 @@
         <v>details</v>
       </c>
     </row>
-    <row r="2">
-      <c r="C2" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -498,9 +498,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/notice.xlsx
+++ b/notice.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,9 +419,26 @@
         <v>details</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Our New Digital Campus is Now Live!</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2026-02-12</v>
+      </c>
+      <c r="C2" t="str">
+        <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
+      </c>
+      <c r="D2" t="str">
+        <v>School</v>
+      </c>
+      <c r="E2" t="str">
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.  What’s new?  Mobile-Friendly Design: No more squinting or awkward zooming; the site looks great on everything from a desktop to a smartphone.  Streamlined Navigation: Access your student portals, fee payments, and academic calendars faster than ever.  Real-Time Updates: A dedicated "News &amp; Events" section to keep you in the loop on holidays, exams, and campus festivities.  Resource Hub: Downloadable forms, syllabi, and digital library links are now organized in one easy-to-find location.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.  What’s new?  Mobile-Friendly Design: No more squinting or awkward zooming; the site looks great on everything from a desktop to a smartphone.  Streamlined Navigation: Access your student portals, fee payments, and academic calendars faster than ever.  Real-Time Updates: A dedicated "News &amp; Events" section to keep you in the loop on holidays, exams, and campus festivities.  Resource Hub: Downloadable forms, syllabi, and digital library links are now organized in one easy-to-find location.</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.         Note to Students &amp; Faculty: If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.         Note to Students &amp; Faculty: If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                          Note to Students &amp; Faculty: If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -421,7 +421,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Our New Digital Campus is Now Live!</v>
+        <v>Our Website is Now Live!</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-12</v>
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                          Note to Students &amp; Faculty: If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                                                                             Note to Students &amp; Faculty: If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                                                                             Note to Students &amp; Faculty: If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                                                                             Note to Students &amp; Faculty:                                                                                               If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                                                                             Note to Students &amp; Faculty:                                                                                               If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -                                                            Note to Students &amp; Faculty:                                                                                               If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -                                                            Note to Students &amp; Faculty:                                                                                               If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -                                                                            If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -                                                                            If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 ------------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -                                                                            If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 ------------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -                                                                            If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                            If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                            If you find any "ghosts in the machine" (broken links or typos), please report and submit at 9761184935 or hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  WhatsApp: +977 9761184935                                                                                                                                                      Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  WhatsApp: +977 9761184935                                                                                                                                                      Email: hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  -------------------------                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                      Email: hello@bbhatt.com.np                                                                                                            -------------------------</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  -------------------------                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                      Email: hello@bbhatt.com.np                                                                                                            -------------------------</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  |---------------------------|                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                      Email: hello@bbhatt.com.np                                                                                                            |---------------------------|</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  |---------------------------|                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                      Email: hello@bbhatt.com.np                                                                                                            |---------------------------|</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  |---------------------------|                                                                                                     |WhatsApp: +977 9761184935  |                                                                                                                                                      |Email: hello@bbhatt.com.np  |                                                                                                          |---------------------------|</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  |---------------------------|                                                                                                     |WhatsApp: +977 9761184935  |                                                                                                                                                      |Email: hello@bbhatt.com.np  |                                                                                                          |---------------------------|</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 -------------------------                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>School</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              -------------------------                                                                           While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -430,7 +430,7 @@
         <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
       </c>
       <c r="D2" t="str">
-        <v>School</v>
+        <v>FileText</v>
       </c>
       <c r="E2" t="str">
         <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -430,7 +430,7 @@
         <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
       </c>
       <c r="D2" t="str">
-        <v>FileText</v>
+        <v>Award</v>
       </c>
       <c r="E2" t="str">
         <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -430,7 +430,7 @@
         <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
       </c>
       <c r="D2" t="str">
-        <v>Award</v>
+        <v>School</v>
       </c>
       <c r="E2" t="str">
         <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -430,7 +430,7 @@
         <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
       </c>
       <c r="D2" t="str">
-        <v>School</v>
+        <v>Bell</v>
       </c>
       <c r="E2" t="str">
         <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
+        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v>After months of hard work and "under construction" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks.                                                                                                 .................................................................                                                                                                             Note to Students &amp; Faculty:                                                                                                                              .................................................................                                                                                                        While we’ve worked hard to ensure a smooth experience, some "ghosts in the machine" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know:                                                                                                                                  ....................................................................                                                                                                     WhatsApp: +977 9761184935                                                                                                                                                        Email: hello@bbhatt.com.np</v>
+        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"center"},{"type":"paragraph","children":[{"text":"Note to Students &amp; Faculty","bold":true,"underline":true}],"align":"center"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}]},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: "},{"text":"+977 9761184935","bold":true}]},{"type":"list-item","children":[{"text":"Email: "},{"text":"hello@bbhatt.com.np","bold":true}]}]}]</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -424,7 +424,7 @@
         <v>Our Website is Now Live!</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-12</v>
+        <v>2082 Falgun 05</v>
       </c>
       <c r="C2" t="str">
         <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"center"},{"type":"paragraph","children":[{"text":"Note to Students &amp; Faculty","bold":true,"underline":true}],"align":"center"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}]},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: "},{"text":"+977 9761184935","bold":true}]},{"type":"list-item","children":[{"text":"Email: "},{"text":"hello@bbhatt.com.np","bold":true}]}]}]</v>
+        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"justify"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty","underline":true}],"align":"left"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}]},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: "},{"text":"+977 9761184935","bold":true}]},{"type":"list-item","children":[{"text":"Email: "},{"text":"hello@bbhatt.com.np","bold":true}]}]}]</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"justify"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty","underline":true}],"align":"left"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}]},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: "},{"text":"+977 9761184935","bold":true}]},{"type":"list-item","children":[{"text":"Email: "},{"text":"hello@bbhatt.com.np","bold":true}]}]}]</v>
+        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"justify"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty"}],"align":"left"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}],"align":"justify"},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: +977 9761184935"}]},{"type":"list-item","children":[{"text":"Email: hello@bbhatt.com.np"}]}]}]</v>
       </c>
     </row>
   </sheetData>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,24 +421,41 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Our Website is Now Live!</v>
+        <v/>
       </c>
       <c r="B2" t="str">
         <v>2082 Falgun 05</v>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Our Website is Now Live!</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2082 Falgun 05</v>
+      </c>
+      <c r="C3" t="str">
         <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D3" t="str">
         <v>Bell</v>
       </c>
-      <c r="E2" t="str">
+      <c r="E3" t="str">
         <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"justify"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty"}],"align":"left"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}],"align":"justify"},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: +977 9761184935"}]},{"type":"list-item","children":[{"text":"Email: hello@bbhatt.com.np"}]}]}]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -400,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -421,41 +421,24 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>Our Website is Now Live!</v>
       </c>
       <c r="B2" t="str">
         <v>2082 Falgun 05</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Our Website is Now Live!</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2082 Falgun 05</v>
-      </c>
-      <c r="C3" t="str">
-        <v>We are proud to announce that our new website is officially LIVE. This platform has been designed to provide a more interactive and seamless experience for our students, parents, and faculty.</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Bell</v>
-      </c>
-      <c r="E3" t="str">
         <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"justify"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty"}],"align":"left"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}],"align":"justify"},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: +977 9761184935"}]},{"type":"list-item","children":[{"text":"Email: hello@bbhatt.com.np"}]}]}]</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/notice.xlsx
+++ b/notice.xlsx
@@ -433,7 +433,7 @@
         <v>Bell</v>
       </c>
       <c r="E2" t="str">
-        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"justify"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty"}],"align":"left"},{"type":"block-quote","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}],"align":"justify"},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: +977 9761184935"}]},{"type":"list-item","children":[{"text":"Email: hello@bbhatt.com.np"}]}]}]</v>
+        <v>[{"type":"paragraph","children":[{"text":"After months of hard work and \"under construction\" signs, we’ve finally pulled back the curtain! Our new website has been redesigned from the ground up to ensure that students, parents, and faculty can find exactly what they need in just a few clicks."}],"align":"left"},{"type":"heading-two","children":[{"text":"Note to Students &amp; Faculty"}],"align":"left"},{"type":"paragraph","children":[{"text":"While we’ve worked hard to ensure a smooth experience, some \"ghosts in the machine\" might still be hiding. If you spot a broken link, a typo, or a technical bug, please let us know."}],"align":"left"},{"type":"bulleted-list","children":[{"type":"list-item","children":[{"text":"WhatsApp: "},{"text":"+977 9761184935","italic":true,"underline":true}]},{"type":"list-item","children":[{"text":"Email: "},{"text":"hello@bbhatt.com.np","italic":true,"underline":true}]}]}]</v>
       </c>
     </row>
   </sheetData>
